--- a/Treinamento/CadastroRestricao.xlsx
+++ b/Treinamento/CadastroRestricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AD2D64-22D2-4B1C-BBB6-EA5DAF910D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1AB812-2EF4-4402-8D89-25D9369EDD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -554,7 +554,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="1" customWidth="1" collapsed="1"/>
@@ -618,22 +618,6 @@
       </c>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Treinamento/CadastroRestricao.xlsx
+++ b/Treinamento/CadastroRestricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6FA551-25B6-41C4-A04D-CAD392E1B7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA487FEE-669B-4124-B342-C02F465954EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Status</t>
   </si>
@@ -59,34 +59,22 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>29/12/2025</t>
-  </si>
-  <si>
-    <t>DYD3826</t>
-  </si>
-  <si>
-    <t>9BFZF10A288110782</t>
-  </si>
-  <si>
     <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
   </si>
   <si>
     <t>Paola Emidio</t>
   </si>
   <si>
-    <t>135995791</t>
-  </si>
-  <si>
-    <t>QUK1312</t>
-  </si>
-  <si>
-    <t>9BGKS69V0KG435466</t>
-  </si>
-  <si>
-    <t>Jacqueline Coelho</t>
-  </si>
-  <si>
-    <t>136016769</t>
+    <t>30/12/2025</t>
+  </si>
+  <si>
+    <t>HCL0351</t>
+  </si>
+  <si>
+    <t>93XLNH77W5C407601</t>
+  </si>
+  <si>
+    <t>135997797</t>
   </si>
 </sst>
 </file>
@@ -608,19 +596,19 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>14</v>
@@ -631,27 +619,7 @@
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">

--- a/Treinamento/CadastroRestricao.xlsx
+++ b/Treinamento/CadastroRestricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF204F96-B26E-4C3F-9384-5DF53B3CF7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71550CA4-44AD-4333-B161-DFF91B3C817E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -554,7 +554,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="1" customWidth="1" collapsed="1"/>
@@ -618,22 +618,6 @@
       </c>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Treinamento/CadastroRestricao.xlsx
+++ b/Treinamento/CadastroRestricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BF3503-4795-4CFF-938E-F568558531F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A936B1-5274-4522-97B3-C3E97E2FCED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,19 +62,19 @@
     <t>21/01/2026</t>
   </si>
   <si>
-    <t>SLV4G77</t>
-  </si>
-  <si>
-    <t>9BGEN48H0RG267847</t>
-  </si>
-  <si>
     <t>ANÁLISE BLOQUEIO 1813 (REVALIDAÇÃO DO NÍVEL DE RISCO)</t>
   </si>
   <si>
-    <t>Priscila Oliveira</t>
-  </si>
-  <si>
-    <t>136296059</t>
+    <t>AZS3177</t>
+  </si>
+  <si>
+    <t>936CLYFY1FB037115</t>
+  </si>
+  <si>
+    <t>Paola Emidio</t>
+  </si>
+  <si>
+    <t>136290645</t>
   </si>
 </sst>
 </file>
@@ -599,13 +599,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>12</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>13</v>

--- a/Treinamento/CadastroRestricao.xlsx
+++ b/Treinamento/CadastroRestricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167F792E-B696-43D3-B455-87CBBBDCA3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9990A60C-4E39-4FA2-B573-49374E90002F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -554,7 +554,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="1" customWidth="1" collapsed="1"/>
@@ -618,22 +618,6 @@
       </c>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Treinamento/CadastroRestricao.xlsx
+++ b/Treinamento/CadastroRestricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395B6E8A-2EB7-44E2-8842-0FF062532876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC9EE7E-A451-4DB3-95FD-DB4245E142E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -554,7 +554,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="1" customWidth="1" collapsed="1"/>
@@ -618,22 +618,6 @@
       </c>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Treinamento/CadastroRestricao.xlsx
+++ b/Treinamento/CadastroRestricao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6240DB-2776-4A82-A3BD-D45246248274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8979243-00F8-489D-85EE-AF2F7727E304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Status</t>
   </si>
@@ -56,9 +56,6 @@
     <t>PROPOSTA</t>
   </si>
   <si>
-    <t>Processar</t>
-  </si>
-  <si>
     <t>24/02/2026</t>
   </si>
   <si>
@@ -75,6 +72,12 @@
   </si>
   <si>
     <t>136766463</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t> Ativação realizada</t>
   </si>
 </sst>
 </file>
@@ -554,7 +557,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="1" customWidth="1" collapsed="1"/>
@@ -596,43 +599,29 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="H2" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
